--- a/MAR_ORIGINAL_RANGO_PRODUCCION.xlsx
+++ b/MAR_ORIGINAL_RANGO_PRODUCCION.xlsx
@@ -95,7 +95,7 @@
     <t>CANTIDADES POR COLORES — MAR ORIGINAL</t>
   </si>
   <si>
-    <t>MAR ORIGINAL CAB · Rango 2764 – 2954 und</t>
+    <t>MAR ORIGINAL CAB · Rango 2400 – 2568 und</t>
   </si>
   <si>
     <t>MÍNIMO — compromiso</t>
@@ -152,7 +152,7 @@
     <t>MÁXIMO — techo</t>
   </si>
   <si>
-    <t>MAR ORIGINAL DAMA · Rango 2545 – 2724 und</t>
+    <t>MAR ORIGINAL DAMA · Rango 2200 – 2355 und</t>
   </si>
   <si>
     <t>Púrpura</t>
@@ -170,7 +170,7 @@
     <t>Morado</t>
   </si>
   <si>
-    <t>MAR ORIGINAL KIDS · Rango 2489 – 2680 und</t>
+    <t>MAR ORIGINAL KIDS · Rango 2700 – 2900 und</t>
   </si>
   <si>
     <t>1</t>
@@ -377,7 +377,7 @@
     <t>★ = tienda con velocidad proyectada/ajustada</t>
   </si>
   <si>
-    <t>CAB · 2764 – 2954 und</t>
+    <t>CAB · 2400 – 2568 und</t>
   </si>
   <si>
     <t>Tienda</t>
@@ -416,10 +416,10 @@
     <t>Vel. mensual proy.</t>
   </si>
   <si>
-    <t>DAMA · 2545 – 2724 und</t>
-  </si>
-  <si>
-    <t>KIDS · 2489 – 2680 und</t>
+    <t>DAMA · 2200 – 2355 und</t>
+  </si>
+  <si>
+    <t>KIDS · 2700 – 2900 und</t>
   </si>
 </sst>
 </file>
@@ -816,13 +816,13 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.1687157894736842</v>
+        <v>0.14</v>
       </c>
       <c r="C6">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="D6">
-        <v>414</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -830,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.2875852631578947</v>
+        <v>0.305</v>
       </c>
       <c r="C7">
-        <v>845</v>
+        <v>733</v>
       </c>
       <c r="D7">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -844,13 +844,13 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.3014559999999999</v>
+        <v>0.342</v>
       </c>
       <c r="C8">
-        <v>946</v>
+        <v>821</v>
       </c>
       <c r="D8">
-        <v>1007</v>
+        <v>875</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -858,13 +858,13 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.1802753684210526</v>
+        <v>0.191</v>
       </c>
       <c r="C9">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="D9">
-        <v>567</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -872,13 +872,13 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0.05043536842105263</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="C10">
+        <v>22</v>
+      </c>
+      <c r="D10">
         <v>25</v>
-      </c>
-      <c r="D10">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -886,13 +886,13 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>0.01037515789473684</v>
+        <v>0.01</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -900,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.0008058947368421055</v>
+        <v>0.002</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -915,10 +915,10 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
-        <v>2764</v>
+        <v>2400</v>
       </c>
       <c r="D13" s="2">
-        <v>2954</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -945,13 +945,13 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <v>0.1820257082896118</v>
+        <v>0.211</v>
       </c>
       <c r="C19">
-        <v>538</v>
+        <v>465</v>
       </c>
       <c r="D19">
-        <v>578</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -959,13 +959,13 @@
         <v>6</v>
       </c>
       <c r="B20">
-        <v>0.2790661070304302</v>
+        <v>0.361</v>
       </c>
       <c r="C20">
-        <v>920</v>
+        <v>795</v>
       </c>
       <c r="D20">
-        <v>982</v>
+        <v>850</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -973,13 +973,13 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>0.2858478488982162</v>
+        <v>0.349</v>
       </c>
       <c r="C21">
-        <v>887</v>
+        <v>767</v>
       </c>
       <c r="D21">
-        <v>948</v>
+        <v>820</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -987,13 +987,13 @@
         <v>8</v>
       </c>
       <c r="B22">
-        <v>0.1731316894018888</v>
+        <v>0.065</v>
       </c>
       <c r="C22">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D22">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1001,13 +1001,13 @@
         <v>9</v>
       </c>
       <c r="B23">
-        <v>0.07968467995802729</v>
+        <v>0.014</v>
       </c>
       <c r="C23">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D23">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1016,10 +1016,10 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
-        <v>2545</v>
+        <v>2200</v>
       </c>
       <c r="D24" s="2">
-        <v>2724</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1046,13 +1046,13 @@
         <v>17</v>
       </c>
       <c r="B30">
-        <v>0.1216101413133832</v>
+        <v>0.129</v>
       </c>
       <c r="C30">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="D30">
-        <v>346</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="B31">
-        <v>0.1205785536159601</v>
+        <v>0.14</v>
       </c>
       <c r="C31">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="D31">
-        <v>377</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1074,13 +1074,13 @@
         <v>19</v>
       </c>
       <c r="B32">
-        <v>0.1654131338320864</v>
+        <v>0.156</v>
       </c>
       <c r="C32">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="D32">
-        <v>420</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1088,13 +1088,13 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>0.1406242726517041</v>
+        <v>0.135</v>
       </c>
       <c r="C33">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="D33">
-        <v>361</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="B34">
-        <v>0.1371005818786367</v>
+        <v>0.126</v>
       </c>
       <c r="C34">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="D34">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1116,13 +1116,13 @@
         <v>22</v>
       </c>
       <c r="B35">
-        <v>0.1571537822111388</v>
+        <v>0.149</v>
       </c>
       <c r="C35">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="D35">
-        <v>399</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1130,13 +1130,13 @@
         <v>23</v>
       </c>
       <c r="B36">
-        <v>0.1578778054862843</v>
+        <v>0.165</v>
       </c>
       <c r="C36">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="D36">
-        <v>442</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1145,10 +1145,10 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2">
-        <v>2489</v>
+        <v>2700</v>
       </c>
       <c r="D37" s="2">
-        <v>2680</v>
+        <v>2900</v>
       </c>
     </row>
   </sheetData>
@@ -1216,16 +1216,16 @@
         <v>0.187</v>
       </c>
       <c r="C6">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D6">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E6">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="F6">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>755</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1248,16 +1248,16 @@
         <v>0.179</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="E7">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1269,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <v>520</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1280,16 +1280,16 @@
         <v>0.147</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F8">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>376</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1312,19 +1312,19 @@
         <v>0.127</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="F9">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>437</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1344,16 +1344,16 @@
         <v>0.104</v>
       </c>
       <c r="C10">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D10">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E10">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>324</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1376,28 +1376,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E11">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F11">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1440,7 +1440,7 @@
         <v>0.038</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1487,13 +1487,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1669,16 +1669,16 @@
         <v>0.187</v>
       </c>
       <c r="C22">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="D22">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="E22">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="F22">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>802</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1701,16 +1701,16 @@
         <v>0.179</v>
       </c>
       <c r="C23">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D23">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="E23">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="F23">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1722,7 +1722,7 @@
         <v>4</v>
       </c>
       <c r="J23">
-        <v>555</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1733,16 +1733,16 @@
         <v>0.147</v>
       </c>
       <c r="C24">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D24">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E24">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F24">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>400</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1765,19 +1765,19 @@
         <v>0.127</v>
       </c>
       <c r="C25">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E25">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="F25">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H25">
         <v>2</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>467</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1797,16 +1797,16 @@
         <v>0.104</v>
       </c>
       <c r="C26">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D26">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="E26">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F26">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>345</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1829,28 +1829,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E27">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F27">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1864,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E28">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="J28">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1893,7 +1893,7 @@
         <v>0.038</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>2</v>
@@ -1940,13 +1940,13 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2121,22 +2121,22 @@
         <v>0.179</v>
       </c>
       <c r="C40">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D40">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E40">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="F40">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2147,22 +2147,22 @@
         <v>0.136</v>
       </c>
       <c r="C41">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D41">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="E41">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F41">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>398</v>
+        <v>344</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2173,22 +2173,22 @@
         <v>0.102</v>
       </c>
       <c r="C42">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D42">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E42">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F42">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G42">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H42">
-        <v>337</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2199,13 +2199,13 @@
         <v>0.095</v>
       </c>
       <c r="C43">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D43">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E43">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2225,13 +2225,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="C44">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D44">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E44">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>206</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2251,13 +2251,13 @@
         <v>0.067</v>
       </c>
       <c r="C45">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D45">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E45">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2277,13 +2277,13 @@
         <v>0.055</v>
       </c>
       <c r="C46">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D46">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E46">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2303,22 +2303,22 @@
         <v>0.055</v>
       </c>
       <c r="C47">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D47">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E47">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F47">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2329,13 +2329,13 @@
         <v>0.05</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D48">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E48">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2355,13 +2355,13 @@
         <v>0.049</v>
       </c>
       <c r="C49">
+        <v>43</v>
+      </c>
+      <c r="D49">
         <v>50</v>
       </c>
-      <c r="D49">
-        <v>58</v>
-      </c>
       <c r="E49">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2381,13 +2381,13 @@
         <v>0.04099999999999999</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D50">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E50">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2407,13 +2407,13 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2433,10 +2433,10 @@
         <v>0.014</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2462,7 +2462,7 @@
         <v>3</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2568,22 +2568,22 @@
         <v>0.179</v>
       </c>
       <c r="C59">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D59">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="E59">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="F59">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>554</v>
+        <v>478</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2594,22 +2594,22 @@
         <v>0.136</v>
       </c>
       <c r="C60">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D60">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E60">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F60">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>423</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2620,22 +2620,22 @@
         <v>0.102</v>
       </c>
       <c r="C61">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D61">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E61">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F61">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G61">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H61">
-        <v>361</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2646,13 +2646,13 @@
         <v>0.095</v>
       </c>
       <c r="C62">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D62">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E62">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>247</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2672,13 +2672,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="C63">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D63">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E63">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2698,13 +2698,13 @@
         <v>0.067</v>
       </c>
       <c r="C64">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D64">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E64">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <v>209</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -2724,13 +2724,13 @@
         <v>0.055</v>
       </c>
       <c r="C65">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D65">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E65">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -2750,22 +2750,22 @@
         <v>0.055</v>
       </c>
       <c r="C66">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D66">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E66">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F66">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2776,13 +2776,13 @@
         <v>0.05</v>
       </c>
       <c r="C67">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D67">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E67">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -2802,13 +2802,13 @@
         <v>0.049</v>
       </c>
       <c r="C68">
+        <v>46</v>
+      </c>
+      <c r="D68">
         <v>53</v>
       </c>
-      <c r="D68">
-        <v>62</v>
-      </c>
       <c r="E68">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="H68">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -2828,13 +2828,13 @@
         <v>0.04099999999999999</v>
       </c>
       <c r="C69">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D69">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E69">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -2854,13 +2854,13 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="C70">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D70">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -2880,10 +2880,10 @@
         <v>0.014</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E71">
         <v>4</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -2909,7 +2909,7 @@
         <v>4</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3029,31 +3029,31 @@
         <v>0.127</v>
       </c>
       <c r="C80">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D80">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E80">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F80">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G80">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H80">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I80">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80">
-        <v>423</v>
+        <v>459</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3064,31 +3064,31 @@
         <v>0.126</v>
       </c>
       <c r="C81">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D81">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E81">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F81">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G81">
         <v>2</v>
       </c>
       <c r="H81">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I81">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <v>415</v>
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3099,31 +3099,31 @@
         <v>0.115</v>
       </c>
       <c r="C82">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D82">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E82">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F82">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G82">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H82">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I82">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82">
-        <v>405</v>
+        <v>440</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3134,31 +3134,31 @@
         <v>0.104</v>
       </c>
       <c r="C83">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D83">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E83">
+        <v>59</v>
+      </c>
+      <c r="F83">
+        <v>42</v>
+      </c>
+      <c r="G83">
+        <v>49</v>
+      </c>
+      <c r="H83">
         <v>54</v>
       </c>
-      <c r="F83">
-        <v>39</v>
-      </c>
-      <c r="G83">
-        <v>45</v>
-      </c>
-      <c r="H83">
-        <v>50</v>
-      </c>
       <c r="I83">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3172,28 +3172,28 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E84">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F84">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G84">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H84">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I84">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
-        <v>236</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3207,19 +3207,19 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E85">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F85">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G85">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H85">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3239,31 +3239,31 @@
         <v>0.08199999999999999</v>
       </c>
       <c r="C86">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D86">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E86">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="G86">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H86">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I86">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3274,31 +3274,31 @@
         <v>0.063</v>
       </c>
       <c r="C87">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E87">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F87">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G87">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H87">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I87">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>180</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3309,13 +3309,13 @@
         <v>0.062</v>
       </c>
       <c r="C88">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3327,13 +3327,13 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3347,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E89">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E91">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3429,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="H91">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I91">
         <v>4</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3449,10 +3449,10 @@
         <v>0.016</v>
       </c>
       <c r="C92">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92">
         <v>2</v>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3629,31 +3629,31 @@
         <v>0.127</v>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D99">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E99">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F99">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G99">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H99">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I99">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
-        <v>452</v>
+        <v>490</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -3664,31 +3664,31 @@
         <v>0.126</v>
       </c>
       <c r="C100">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D100">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E100">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F100">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G100">
         <v>3</v>
       </c>
       <c r="H100">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I100">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <v>445</v>
+        <v>480</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -3699,31 +3699,31 @@
         <v>0.115</v>
       </c>
       <c r="C101">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D101">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E101">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F101">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G101">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H101">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I101">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
-        <v>433</v>
+        <v>470</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -3734,31 +3734,31 @@
         <v>0.104</v>
       </c>
       <c r="C102">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D102">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E102">
+        <v>63</v>
+      </c>
+      <c r="F102">
+        <v>45</v>
+      </c>
+      <c r="G102">
+        <v>52</v>
+      </c>
+      <c r="H102">
         <v>58</v>
       </c>
-      <c r="F102">
-        <v>42</v>
-      </c>
-      <c r="G102">
-        <v>48</v>
-      </c>
-      <c r="H102">
-        <v>53</v>
-      </c>
       <c r="I102">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -3772,28 +3772,28 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E103">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F103">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G103">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H103">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I103">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -3807,19 +3807,19 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E104">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F104">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G104">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H104">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -3839,31 +3839,31 @@
         <v>0.08199999999999999</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D105">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E105">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F105">
         <v>0</v>
       </c>
       <c r="G105">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H105">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I105">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -3874,31 +3874,31 @@
         <v>0.063</v>
       </c>
       <c r="C106">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D106">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E106">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F106">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G106">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H106">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I106">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -3909,13 +3909,13 @@
         <v>0.062</v>
       </c>
       <c r="C107">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -3927,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3962,13 +3962,13 @@
         <v>3</v>
       </c>
       <c r="I108">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E110">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="H110">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I110">
         <v>5</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4049,10 +4049,10 @@
         <v>0.016</v>
       </c>
       <c r="C111">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D111">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E111">
         <v>3</v>
@@ -4067,13 +4067,13 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4228,62 +4228,62 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="C6">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="D6">
-        <v>41.7</v>
+        <v>55.6</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="C7">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="D7">
-        <v>55.6</v>
+        <v>54.9</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="C8">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="D8">
-        <v>54.9</v>
+        <v>41.7</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4291,10 +4291,10 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C9">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D9">
         <v>37.9</v>
@@ -4311,10 +4311,10 @@
         <v>61</v>
       </c>
       <c r="B10">
-        <v>755</v>
+        <v>656</v>
       </c>
       <c r="C10">
-        <v>802</v>
+        <v>696</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4344,22 +4344,22 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="C14">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="D14">
-        <v>27.2</v>
+        <v>57.5</v>
       </c>
       <c r="E14">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="F14">
-        <v>2.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4367,10 +4367,10 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C15">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D15">
         <v>45.5</v>
@@ -4384,42 +4384,42 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="C16">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="D16">
-        <v>57.5</v>
+        <v>27.3</v>
       </c>
       <c r="E16">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="D17">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="E17">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="F17">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4447,10 +4447,10 @@
         <v>61</v>
       </c>
       <c r="B19">
-        <v>520</v>
+        <v>452</v>
       </c>
       <c r="C19">
-        <v>555</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4480,42 +4480,42 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C23">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D23">
-        <v>32.2</v>
+        <v>42.9</v>
       </c>
       <c r="E23">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F23">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B24">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C24">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="D24">
-        <v>42.9</v>
+        <v>35.5</v>
       </c>
       <c r="E24">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4523,10 +4523,10 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C25">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>39.8</v>
@@ -4540,22 +4540,22 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B26">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C26">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D26">
-        <v>35.5</v>
+        <v>32.2</v>
       </c>
       <c r="E26">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F26">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4563,10 +4563,10 @@
         <v>61</v>
       </c>
       <c r="B27">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C27">
-        <v>400</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4596,82 +4596,82 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="C31">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="D31">
-        <v>16.7</v>
+        <v>41.2</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B32">
+        <v>84</v>
+      </c>
+      <c r="C32">
         <v>90</v>
       </c>
-      <c r="C32">
-        <v>96</v>
-      </c>
       <c r="D32">
-        <v>33</v>
+        <v>22.3</v>
       </c>
       <c r="E32">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="C33">
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="D33">
-        <v>41.2</v>
+        <v>33</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F33">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C34">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="D34">
-        <v>22.3</v>
+        <v>16.7</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4679,10 +4679,10 @@
         <v>10</v>
       </c>
       <c r="B35">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D35">
         <v>10.9</v>
@@ -4719,10 +4719,10 @@
         <v>61</v>
       </c>
       <c r="B37">
-        <v>437</v>
+        <v>379</v>
       </c>
       <c r="C37">
-        <v>467</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4752,62 +4752,62 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="C41">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="D41">
-        <v>17.9</v>
+        <v>32.7</v>
       </c>
       <c r="E41">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F41">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="C42">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D42">
-        <v>32.7</v>
+        <v>29.2</v>
       </c>
       <c r="E42">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B43">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="C43">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="D43">
-        <v>29.2</v>
+        <v>17.9</v>
       </c>
       <c r="E43">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F43">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4815,10 +4815,10 @@
         <v>9</v>
       </c>
       <c r="B44">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C44">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D44">
         <v>16</v>
@@ -4835,10 +4835,10 @@
         <v>61</v>
       </c>
       <c r="B45">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="C45">
-        <v>345</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4868,42 +4868,42 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D49">
-        <v>10.3</v>
+        <v>21.7</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B50">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C50">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D50">
-        <v>21.7</v>
+        <v>13.6</v>
       </c>
       <c r="E50">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4911,10 +4911,10 @@
         <v>8</v>
       </c>
       <c r="B51">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C51">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D51">
         <v>18.1</v>
@@ -4928,22 +4928,22 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B52">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D52">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="E52">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4951,10 +4951,10 @@
         <v>11</v>
       </c>
       <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53">
         <v>9</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
       </c>
       <c r="D53">
         <v>2.7</v>
@@ -4971,10 +4971,10 @@
         <v>61</v>
       </c>
       <c r="B54">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C54">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -5007,10 +5007,10 @@
         <v>7</v>
       </c>
       <c r="B58">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C58">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D58">
         <v>17</v>
@@ -5027,10 +5027,10 @@
         <v>8</v>
       </c>
       <c r="B59">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C59">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D59">
         <v>14.5</v>
@@ -5047,10 +5047,10 @@
         <v>9</v>
       </c>
       <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
         <v>9</v>
-      </c>
-      <c r="C60">
-        <v>10</v>
       </c>
       <c r="D60">
         <v>8</v>
@@ -5107,10 +5107,10 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C63">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5143,10 +5143,10 @@
         <v>6</v>
       </c>
       <c r="B67">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C67">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D67">
         <v>8.6</v>
@@ -5183,10 +5183,10 @@
         <v>61</v>
       </c>
       <c r="B69">
+        <v>14</v>
+      </c>
+      <c r="C69">
         <v>16</v>
-      </c>
-      <c r="C69">
-        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -5219,10 +5219,10 @@
         <v>8</v>
       </c>
       <c r="B73">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C73">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D73">
         <v>9.5</v>
@@ -5236,42 +5236,42 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74">
         <v>9</v>
       </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
       <c r="C74">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D74">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>2.6</v>
+      </c>
+      <c r="E75">
         <v>10</v>
       </c>
-      <c r="C75">
-        <v>11</v>
-      </c>
-      <c r="D75">
-        <v>1.9</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
       <c r="F75">
-        <v>0</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5279,10 +5279,10 @@
         <v>61</v>
       </c>
       <c r="B76">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C76">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5561,62 +5561,62 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="C103">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="D103">
-        <v>16.1</v>
+        <v>43</v>
       </c>
       <c r="E103">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F103">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B104">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C104">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="D104">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="E104">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F104">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B105">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="C105">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="D105">
-        <v>42.6</v>
+        <v>16.1</v>
       </c>
       <c r="E105">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F105">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -5624,10 +5624,10 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C106">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D106">
         <v>27.4</v>
@@ -5644,10 +5644,10 @@
         <v>61</v>
       </c>
       <c r="B107">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="C107">
-        <v>554</v>
+        <v>478</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -5677,19 +5677,19 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B111">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C111">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="D111">
-        <v>22.8</v>
+        <v>34.4</v>
       </c>
       <c r="E111">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F111">
         <v>0.7</v>
@@ -5697,42 +5697,42 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C112">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="D112">
-        <v>34.4</v>
+        <v>27.3</v>
       </c>
       <c r="E112">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F112">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B113">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="C113">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="D113">
-        <v>27.3</v>
+        <v>22.8</v>
       </c>
       <c r="E113">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F113">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5740,10 +5740,10 @@
         <v>8</v>
       </c>
       <c r="B114">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C114">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D114">
         <v>17.3</v>
@@ -5760,10 +5760,10 @@
         <v>61</v>
       </c>
       <c r="B115">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="C115">
-        <v>423</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5793,22 +5793,22 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B119">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C119">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="D119">
-        <v>4.8</v>
+        <v>22.2</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F119">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5816,10 +5816,10 @@
         <v>6</v>
       </c>
       <c r="B120">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C120">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D120">
         <v>20.5</v>
@@ -5833,62 +5833,62 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B121">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="C121">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="D121">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="E121">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="F121">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B122">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C122">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D122">
-        <v>22.5</v>
+        <v>17</v>
       </c>
       <c r="E122">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F122">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B123">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C123">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D123">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="E123">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F123">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5896,10 +5896,10 @@
         <v>61</v>
       </c>
       <c r="B124">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="C124">
-        <v>361</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5929,22 +5929,22 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B128">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="C128">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="D128">
-        <v>10.5</v>
+        <v>28.8</v>
       </c>
       <c r="E128">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F128">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5952,10 +5952,10 @@
         <v>6</v>
       </c>
       <c r="B129">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C129">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D129">
         <v>19.9</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B130">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C130">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D130">
-        <v>28.8</v>
+        <v>10.5</v>
       </c>
       <c r="E130">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F130">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5992,10 +5992,10 @@
         <v>61</v>
       </c>
       <c r="B131">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="C131">
-        <v>247</v>
+        <v>214</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6025,39 +6025,39 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B135">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C135">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D135">
-        <v>17.7</v>
+        <v>19.2</v>
       </c>
       <c r="E135">
         <v>19</v>
       </c>
       <c r="F135">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B136">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C136">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D136">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="E136">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F136">
         <v>1.1</v>
@@ -6065,22 +6065,22 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B137">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C137">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D137">
-        <v>19.2</v>
+        <v>16.9</v>
       </c>
       <c r="E137">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6088,10 +6088,10 @@
         <v>61</v>
       </c>
       <c r="B138">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C138">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6121,22 +6121,22 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B142">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C142">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D142">
-        <v>10.4</v>
+        <v>16.5</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F142">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6144,10 +6144,10 @@
         <v>6</v>
       </c>
       <c r="B143">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C143">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D143">
         <v>12.8</v>
@@ -6161,22 +6161,22 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B144">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C144">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D144">
-        <v>16.5</v>
+        <v>10.4</v>
       </c>
       <c r="E144">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F144">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -6184,10 +6184,10 @@
         <v>61</v>
       </c>
       <c r="B145">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C145">
-        <v>209</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -6217,42 +6217,42 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B149">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C149">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D149">
-        <v>10.5</v>
+        <v>13.2</v>
       </c>
       <c r="E149">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F149">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B150">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C150">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D150">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="E150">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F150">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -6260,10 +6260,10 @@
         <v>7</v>
       </c>
       <c r="B151">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C151">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D151">
         <v>9.199999999999999</v>
@@ -6280,10 +6280,10 @@
         <v>61</v>
       </c>
       <c r="B152">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C152">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -6313,62 +6313,62 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B156">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C156">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D156">
-        <v>8.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="E156">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F156">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B157">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C157">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D157">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B158">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C158">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D158">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F158">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -6376,10 +6376,10 @@
         <v>8</v>
       </c>
       <c r="B159">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C159">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D159">
         <v>7.7</v>
@@ -6396,10 +6396,10 @@
         <v>61</v>
       </c>
       <c r="B160">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C160">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -6429,22 +6429,22 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B164">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C164">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D164">
-        <v>6.1</v>
+        <v>16.7</v>
       </c>
       <c r="E164">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F164">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -6452,10 +6452,10 @@
         <v>6</v>
       </c>
       <c r="B165">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C165">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D165">
         <v>7.6</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B166">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="C166">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D166">
-        <v>16.7</v>
+        <v>6.1</v>
       </c>
       <c r="E166">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F166">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -6492,10 +6492,10 @@
         <v>61</v>
       </c>
       <c r="B167">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C167">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -6525,7 +6525,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B171">
         <v>50</v>
@@ -6534,33 +6534,33 @@
         <v>53</v>
       </c>
       <c r="D171">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="E171">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F171">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B172">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C172">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D172">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F172">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -6568,10 +6568,10 @@
         <v>7</v>
       </c>
       <c r="B173">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C173">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D173">
         <v>8.800000000000001</v>
@@ -6588,10 +6588,10 @@
         <v>61</v>
       </c>
       <c r="B174">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C174">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -6621,42 +6621,42 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B178">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C178">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D178">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="E178">
         <v>16</v>
       </c>
       <c r="F178">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B179">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C179">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D179">
-        <v>9.5</v>
+        <v>6.9</v>
       </c>
       <c r="E179">
         <v>16</v>
       </c>
       <c r="F179">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6664,10 +6664,10 @@
         <v>7</v>
       </c>
       <c r="B180">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C180">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D180">
         <v>8.6</v>
@@ -6684,10 +6684,10 @@
         <v>61</v>
       </c>
       <c r="B181">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C181">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6720,10 +6720,10 @@
         <v>15</v>
       </c>
       <c r="B185">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C185">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D185">
         <v>8.5</v>
@@ -6740,10 +6740,10 @@
         <v>6</v>
       </c>
       <c r="B186">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C186">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D186">
         <v>8</v>
@@ -6760,10 +6760,10 @@
         <v>7</v>
       </c>
       <c r="B187">
+        <v>5</v>
+      </c>
+      <c r="C187">
         <v>6</v>
-      </c>
-      <c r="C187">
-        <v>7</v>
       </c>
       <c r="D187">
         <v>7.5</v>
@@ -6780,10 +6780,10 @@
         <v>61</v>
       </c>
       <c r="B188">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C188">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6813,42 +6813,42 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B192">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C192">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D192">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193">
         <v>6</v>
       </c>
-      <c r="B193">
-        <v>10</v>
-      </c>
       <c r="C193">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D193">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F193">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -6876,10 +6876,10 @@
         <v>61</v>
       </c>
       <c r="B195">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C195">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6909,16 +6909,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C199">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D199">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6929,16 +6929,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B200">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C200">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D200">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6972,10 +6972,10 @@
         <v>61</v>
       </c>
       <c r="B202">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C202">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -7008,10 +7008,10 @@
         <v>7</v>
       </c>
       <c r="B206">
+        <v>4</v>
+      </c>
+      <c r="C206">
         <v>5</v>
-      </c>
-      <c r="C206">
-        <v>6</v>
       </c>
       <c r="D206">
         <v>0.8</v>
@@ -7028,10 +7028,10 @@
         <v>61</v>
       </c>
       <c r="B207">
+        <v>4</v>
+      </c>
+      <c r="C207">
         <v>5</v>
-      </c>
-      <c r="C207">
-        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -7122,22 +7122,22 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B218">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="C218">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D218">
-        <v>8.5</v>
+        <v>17.7</v>
       </c>
       <c r="E218">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F218">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -7145,10 +7145,10 @@
         <v>18</v>
       </c>
       <c r="B219">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C219">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D219">
         <v>10.7</v>
@@ -7165,10 +7165,10 @@
         <v>19</v>
       </c>
       <c r="B220">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C220">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D220">
         <v>9.5</v>
@@ -7182,42 +7182,42 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B221">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C221">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D221">
-        <v>11.7</v>
+        <v>12.6</v>
       </c>
       <c r="E221">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F221">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B222">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C222">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D222">
-        <v>17.7</v>
+        <v>11.7</v>
       </c>
       <c r="E222">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F222">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -7225,10 +7225,10 @@
         <v>22</v>
       </c>
       <c r="B223">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C223">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D223">
         <v>9.800000000000001</v>
@@ -7242,22 +7242,22 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B224">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C224">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D224">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="E224">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F224">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -7265,10 +7265,10 @@
         <v>61</v>
       </c>
       <c r="B225">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="C225">
-        <v>452</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -7298,19 +7298,19 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B229">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C229">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D229">
-        <v>11.2</v>
+        <v>13.8</v>
       </c>
       <c r="E229">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F229">
         <v>0.8</v>
@@ -7318,122 +7318,122 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B230">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C230">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D230">
-        <v>11.2</v>
+        <v>14.2</v>
       </c>
       <c r="E230">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F230">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B231">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C231">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D231">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="E231">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F231">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B232">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C232">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D232">
-        <v>14.2</v>
+        <v>11.2</v>
       </c>
       <c r="E232">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F232">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
+        <v>19</v>
+      </c>
+      <c r="B233">
+        <v>62</v>
+      </c>
+      <c r="C233">
+        <v>66</v>
+      </c>
+      <c r="D233">
+        <v>11.8</v>
+      </c>
+      <c r="E233">
         <v>21</v>
       </c>
-      <c r="B233">
-        <v>2</v>
-      </c>
-      <c r="C233">
-        <v>3</v>
-      </c>
-      <c r="D233">
-        <v>6</v>
-      </c>
-      <c r="E233">
-        <v>29</v>
-      </c>
       <c r="F233">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B234">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C234">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D234">
-        <v>13.8</v>
+        <v>12</v>
       </c>
       <c r="E234">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F234">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B235">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C235">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="D235">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E235">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F235">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -7441,10 +7441,10 @@
         <v>61</v>
       </c>
       <c r="B236">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="C236">
-        <v>445</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -7474,62 +7474,62 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B240">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="C240">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="E240">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F240">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B241">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C241">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D241">
-        <v>6.1</v>
+        <v>12.4</v>
       </c>
       <c r="E241">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F241">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B242">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C242">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D242">
-        <v>6.4</v>
+        <v>10.7</v>
       </c>
       <c r="E242">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F242">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -7537,10 +7537,10 @@
         <v>20</v>
       </c>
       <c r="B243">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C243">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D243">
         <v>11.3</v>
@@ -7554,62 +7554,62 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B244">
+        <v>55</v>
+      </c>
+      <c r="C244">
         <v>59</v>
       </c>
-      <c r="C244">
-        <v>63</v>
-      </c>
       <c r="D244">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="E244">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F244">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B245">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C245">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D245">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="E245">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F245">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B246">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="C246">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="D246">
-        <v>16.5</v>
+        <v>6.1</v>
       </c>
       <c r="E246">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F246">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -7617,10 +7617,10 @@
         <v>61</v>
       </c>
       <c r="B247">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="C247">
-        <v>433</v>
+        <v>470</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -7653,10 +7653,10 @@
         <v>17</v>
       </c>
       <c r="B251">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C251">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D251">
         <v>10.1</v>
@@ -7670,27 +7670,27 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B252">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C252">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D252">
-        <v>7.2</v>
+        <v>11.4</v>
       </c>
       <c r="E252">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F252">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B253">
         <v>54</v>
@@ -7699,73 +7699,73 @@
         <v>58</v>
       </c>
       <c r="D253">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="E253">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F253">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B254">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C254">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D254">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="E254">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F254">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B255">
+        <v>42</v>
+      </c>
+      <c r="C255">
         <v>45</v>
       </c>
-      <c r="C255">
-        <v>48</v>
-      </c>
       <c r="D255">
-        <v>10.4</v>
+        <v>7.2</v>
       </c>
       <c r="E255">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F255">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B256">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C256">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D256">
-        <v>11.1</v>
+        <v>7.2</v>
       </c>
       <c r="E256">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F256">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7773,10 +7773,10 @@
         <v>23</v>
       </c>
       <c r="B257">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C257">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D257">
         <v>8.800000000000001</v>
@@ -7793,10 +7793,10 @@
         <v>61</v>
       </c>
       <c r="B258">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C258">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7826,122 +7826,122 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B262">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C262">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="D262">
-        <v>7.5</v>
+        <v>10.4</v>
       </c>
       <c r="E262">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F262">
-        <v>6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B263">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C263">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D263">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="E263">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F263">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B264">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C264">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D264">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E264">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F264">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B265">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C265">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D265">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="E265">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F265">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B266">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C266">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D266">
-        <v>10.6</v>
+        <v>9.9</v>
       </c>
       <c r="E266">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F266">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B267">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C267">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D267">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="E267">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F267">
-        <v>1.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7949,10 +7949,10 @@
         <v>61</v>
       </c>
       <c r="B268">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C268">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7985,10 +7985,10 @@
         <v>18</v>
       </c>
       <c r="B272">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C272">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D272">
         <v>10.2</v>
@@ -8005,10 +8005,10 @@
         <v>19</v>
       </c>
       <c r="B273">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C273">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D273">
         <v>11.8</v>
@@ -8025,10 +8025,10 @@
         <v>20</v>
       </c>
       <c r="B274">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C274">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D274">
         <v>11.1</v>
@@ -8042,42 +8042,42 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
+        <v>22</v>
+      </c>
+      <c r="B275">
         <v>21</v>
       </c>
-      <c r="B275">
-        <v>15</v>
-      </c>
       <c r="C275">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D275">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E275">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F275">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B276">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C276">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D276">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E276">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F276">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -8085,10 +8085,10 @@
         <v>61</v>
       </c>
       <c r="B277">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C277">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -8121,10 +8121,10 @@
         <v>17</v>
       </c>
       <c r="B281">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C281">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D281">
         <v>7.7</v>
@@ -8141,10 +8141,10 @@
         <v>18</v>
       </c>
       <c r="B282">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C282">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D282">
         <v>5.8</v>
@@ -8158,42 +8158,42 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B283">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C283">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D283">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="E283">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F283">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
+        <v>19</v>
+      </c>
+      <c r="B284">
+        <v>19</v>
+      </c>
+      <c r="C284">
         <v>21</v>
       </c>
-      <c r="B284">
-        <v>15</v>
-      </c>
-      <c r="C284">
-        <v>16</v>
-      </c>
       <c r="D284">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="E284">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F284">
-        <v>5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -8201,10 +8201,10 @@
         <v>22</v>
       </c>
       <c r="B285">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C285">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D285">
         <v>8.4</v>
@@ -8218,22 +8218,22 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B286">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C286">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D286">
-        <v>11.6</v>
+        <v>7.3</v>
       </c>
       <c r="E286">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F286">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -8241,10 +8241,10 @@
         <v>61</v>
       </c>
       <c r="B287">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C287">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -8277,10 +8277,10 @@
         <v>17</v>
       </c>
       <c r="B291">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C291">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D291">
         <v>6.4</v>
@@ -8294,42 +8294,42 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B292">
+        <v>39</v>
+      </c>
+      <c r="C292">
+        <v>42</v>
+      </c>
+      <c r="D292">
         <v>6</v>
       </c>
-      <c r="C292">
-        <v>7</v>
-      </c>
-      <c r="D292">
-        <v>2.4</v>
-      </c>
       <c r="E292">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F292">
-        <v>3.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B293">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C293">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E293">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -8337,10 +8337,10 @@
         <v>20</v>
       </c>
       <c r="B294">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C294">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D294">
         <v>5.9</v>
@@ -8354,62 +8354,62 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B295">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C295">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D295">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="E295">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F295">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B296">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C296">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D296">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="E296">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F296">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B297">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C297">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D297">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="E297">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F297">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -8417,10 +8417,10 @@
         <v>61</v>
       </c>
       <c r="B298">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C298">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -8453,10 +8453,10 @@
         <v>17</v>
       </c>
       <c r="B302">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C302">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D302">
         <v>7.4</v>
@@ -8470,42 +8470,42 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
+        <v>23</v>
+      </c>
+      <c r="B303">
+        <v>17</v>
+      </c>
+      <c r="C303">
         <v>19</v>
       </c>
-      <c r="B303">
-        <v>6</v>
-      </c>
-      <c r="C303">
-        <v>7</v>
-      </c>
       <c r="D303">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="E303">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F303">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B304">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C304">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D304">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="E304">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F304">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -8513,10 +8513,10 @@
         <v>61</v>
       </c>
       <c r="B305">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C305">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -8546,82 +8546,82 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B309">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C309">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D309">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="E309">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F309">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B310">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C310">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D310">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="E310">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F310">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B311">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C311">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D311">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="E311">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F311">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B312">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C312">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D312">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="E312">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F312">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -8629,10 +8629,10 @@
         <v>61</v>
       </c>
       <c r="B313">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C313">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -8662,42 +8662,42 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B317">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C317">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D317">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="E317">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F317">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B318">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C318">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D318">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="E318">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F318">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8705,10 +8705,10 @@
         <v>61</v>
       </c>
       <c r="B319">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C319">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8738,42 +8738,42 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B323">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C323">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D323">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="E323">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F323">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
+        <v>18</v>
+      </c>
+      <c r="B324">
+        <v>17</v>
+      </c>
+      <c r="C324">
         <v>19</v>
       </c>
-      <c r="B324">
-        <v>27</v>
-      </c>
-      <c r="C324">
-        <v>29</v>
-      </c>
       <c r="D324">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="E324">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F324">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8781,10 +8781,10 @@
         <v>22</v>
       </c>
       <c r="B325">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C325">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D325">
         <v>1.5</v>
@@ -8821,10 +8821,10 @@
         <v>61</v>
       </c>
       <c r="B327">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C327">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8857,10 +8857,10 @@
         <v>17</v>
       </c>
       <c r="B331">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C331">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D331">
         <v>4.3</v>
@@ -8877,10 +8877,10 @@
         <v>18</v>
       </c>
       <c r="B332">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C332">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D332">
         <v>2.2</v>
@@ -8894,42 +8894,42 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B333">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C333">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D333">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="E333">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F333">
-        <v>4.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B334">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C334">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="E334">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F334">
-        <v>1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8937,10 +8937,10 @@
         <v>61</v>
       </c>
       <c r="B335">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C335">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -9191,22 +9191,22 @@
         <v>0.187</v>
       </c>
       <c r="D5">
-        <v>755</v>
+        <v>656</v>
       </c>
       <c r="E5">
-        <v>802</v>
+        <v>696</v>
       </c>
       <c r="F5">
-        <v>377.5</v>
+        <v>328</v>
       </c>
       <c r="G5">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="H5">
-        <v>453</v>
+        <v>393.6</v>
       </c>
       <c r="I5">
-        <v>481.2</v>
+        <v>417.6</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9220,22 +9220,22 @@
         <v>0.179</v>
       </c>
       <c r="D6">
-        <v>520</v>
+        <v>452</v>
       </c>
       <c r="E6">
-        <v>555</v>
+        <v>482</v>
       </c>
       <c r="F6">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="G6">
-        <v>277.5</v>
+        <v>241</v>
       </c>
       <c r="H6">
-        <v>312</v>
+        <v>271.2</v>
       </c>
       <c r="I6">
-        <v>333</v>
+        <v>289.2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9249,22 +9249,22 @@
         <v>0.147</v>
       </c>
       <c r="D7">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="E7">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="F7">
-        <v>188</v>
+        <v>162.5</v>
       </c>
       <c r="G7">
-        <v>200</v>
+        <v>173.5</v>
       </c>
       <c r="H7">
-        <v>225.6</v>
+        <v>195</v>
       </c>
       <c r="I7">
-        <v>240</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -9278,22 +9278,22 @@
         <v>0.127</v>
       </c>
       <c r="D8">
-        <v>437</v>
+        <v>379</v>
       </c>
       <c r="E8">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="F8">
-        <v>218.5</v>
+        <v>189.5</v>
       </c>
       <c r="G8">
-        <v>233.5</v>
+        <v>202.5</v>
       </c>
       <c r="H8">
-        <v>262.2</v>
+        <v>227.4</v>
       </c>
       <c r="I8">
-        <v>280.2</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -9307,22 +9307,22 @@
         <v>0.104</v>
       </c>
       <c r="D9">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="E9">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="F9">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="G9">
-        <v>172.5</v>
+        <v>149.5</v>
       </c>
       <c r="H9">
-        <v>194.4</v>
+        <v>168</v>
       </c>
       <c r="I9">
-        <v>207</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -9336,22 +9336,22 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="D10">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E10">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="F10">
-        <v>88.5</v>
+        <v>77</v>
       </c>
       <c r="G10">
-        <v>95</v>
+        <v>82.5</v>
       </c>
       <c r="H10">
-        <v>106.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I10">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -9365,22 +9365,22 @@
         <v>0.05599999999999999</v>
       </c>
       <c r="D11">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="F11">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G11">
-        <v>58.5</v>
+        <v>51.5</v>
       </c>
       <c r="H11">
-        <v>64.8</v>
+        <v>56.4</v>
       </c>
       <c r="I11">
-        <v>70.2</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -9394,22 +9394,22 @@
         <v>0.038</v>
       </c>
       <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
         <v>16</v>
       </c>
-      <c r="E12">
-        <v>18</v>
-      </c>
       <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
         <v>8</v>
       </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
       <c r="H12">
+        <v>8.4</v>
+      </c>
+      <c r="I12">
         <v>9.6</v>
-      </c>
-      <c r="I12">
-        <v>10.8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -9423,22 +9423,22 @@
         <v>0.025</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="G13">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="H13">
-        <v>22.8</v>
+        <v>19.8</v>
       </c>
       <c r="I13">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -9568,22 +9568,22 @@
         <v>0.179</v>
       </c>
       <c r="D18">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="E18">
-        <v>554</v>
+        <v>478</v>
       </c>
       <c r="F18">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="G18">
-        <v>221.6</v>
+        <v>191.2</v>
       </c>
       <c r="H18">
-        <v>249.6</v>
+        <v>216</v>
       </c>
       <c r="I18">
-        <v>265.92</v>
+        <v>229.44</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -9597,22 +9597,22 @@
         <v>0.136</v>
       </c>
       <c r="D19">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="E19">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="F19">
-        <v>159.2</v>
+        <v>137.6</v>
       </c>
       <c r="G19">
-        <v>169.2</v>
+        <v>146.4</v>
       </c>
       <c r="H19">
-        <v>191.04</v>
+        <v>165.12</v>
       </c>
       <c r="I19">
-        <v>203.04</v>
+        <v>175.68</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -9626,22 +9626,22 @@
         <v>0.102</v>
       </c>
       <c r="D20">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="E20">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="F20">
-        <v>134.8</v>
+        <v>116.8</v>
       </c>
       <c r="G20">
-        <v>144.4</v>
+        <v>124.8</v>
       </c>
       <c r="H20">
-        <v>161.76</v>
+        <v>140.16</v>
       </c>
       <c r="I20">
-        <v>173.28</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -9655,22 +9655,22 @@
         <v>0.095</v>
       </c>
       <c r="D21">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="E21">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="F21">
-        <v>92.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G21">
-        <v>98.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H21">
-        <v>110.88</v>
+        <v>96</v>
       </c>
       <c r="I21">
-        <v>118.56</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -9684,22 +9684,22 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D22">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E22">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="F22">
-        <v>82.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G22">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H22">
-        <v>98.88</v>
+        <v>85.44</v>
       </c>
       <c r="I22">
-        <v>105.6</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -9713,22 +9713,22 @@
         <v>0.067</v>
       </c>
       <c r="D23">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="E23">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="F23">
-        <v>78.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G23">
-        <v>83.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H23">
-        <v>94.08</v>
+        <v>81.12</v>
       </c>
       <c r="I23">
-        <v>100.32</v>
+        <v>86.88</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -9742,22 +9742,22 @@
         <v>0.055</v>
       </c>
       <c r="D24">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E24">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F24">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
       <c r="G24">
-        <v>50.4</v>
+        <v>43.2</v>
       </c>
       <c r="H24">
-        <v>56.16</v>
+        <v>48.48</v>
       </c>
       <c r="I24">
-        <v>60.48</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -9771,22 +9771,22 @@
         <v>0.055</v>
       </c>
       <c r="D25">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E25">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="F25">
-        <v>55.6</v>
+        <v>47.6</v>
       </c>
       <c r="G25">
-        <v>59.6</v>
+        <v>51.2</v>
       </c>
       <c r="H25">
-        <v>66.72</v>
+        <v>57.12</v>
       </c>
       <c r="I25">
-        <v>71.52</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -9800,22 +9800,22 @@
         <v>0.05</v>
       </c>
       <c r="D26">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E26">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F26">
-        <v>38.4</v>
+        <v>33.2</v>
       </c>
       <c r="G26">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="H26">
-        <v>46.08</v>
+        <v>39.84</v>
       </c>
       <c r="I26">
-        <v>49.44</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -9829,22 +9829,22 @@
         <v>0.049</v>
       </c>
       <c r="D27">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="E27">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F27">
-        <v>56.4</v>
+        <v>48.8</v>
       </c>
       <c r="G27">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H27">
-        <v>67.68000000000001</v>
+        <v>58.56</v>
       </c>
       <c r="I27">
-        <v>72</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -9858,22 +9858,22 @@
         <v>0.04099999999999999</v>
       </c>
       <c r="D28">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E28">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>23.2</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>24.8</v>
+        <v>21.6</v>
       </c>
       <c r="H28">
-        <v>27.84</v>
+        <v>24</v>
       </c>
       <c r="I28">
-        <v>29.76</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -9887,22 +9887,22 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="D29">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E29">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F29">
-        <v>27.6</v>
+        <v>23.6</v>
       </c>
       <c r="G29">
-        <v>30</v>
+        <v>25.6</v>
       </c>
       <c r="H29">
-        <v>33.12</v>
+        <v>28.32</v>
       </c>
       <c r="I29">
-        <v>36</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -9916,22 +9916,22 @@
         <v>0.014</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="G30">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H30">
-        <v>9.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I30">
-        <v>11.04</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -9945,22 +9945,22 @@
         <v>0.002</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G31">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H31">
-        <v>4.8</v>
+        <v>4.32</v>
       </c>
       <c r="I31">
-        <v>6.24</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -9974,22 +9974,22 @@
         <v>0.001</v>
       </c>
       <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
         <v>5</v>
       </c>
-      <c r="E32">
-        <v>6</v>
-      </c>
       <c r="F32">
+        <v>1.6</v>
+      </c>
+      <c r="G32">
         <v>2</v>
       </c>
-      <c r="G32">
+      <c r="H32">
+        <v>1.92</v>
+      </c>
+      <c r="I32">
         <v>2.4</v>
-      </c>
-      <c r="H32">
-        <v>2.4</v>
-      </c>
-      <c r="I32">
-        <v>2.88</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -10032,22 +10032,22 @@
         <v>0.127</v>
       </c>
       <c r="D34">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="E34">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="F34">
-        <v>109.98</v>
+        <v>119.34</v>
       </c>
       <c r="G34">
-        <v>117.52</v>
+        <v>127.4</v>
       </c>
       <c r="H34">
-        <v>131.98</v>
+        <v>143.21</v>
       </c>
       <c r="I34">
-        <v>141.02</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -10061,22 +10061,22 @@
         <v>0.126</v>
       </c>
       <c r="D35">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="E35">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="F35">
-        <v>107.9</v>
+        <v>116.74</v>
       </c>
       <c r="G35">
-        <v>115.7</v>
+        <v>124.8</v>
       </c>
       <c r="H35">
-        <v>129.48</v>
+        <v>140.09</v>
       </c>
       <c r="I35">
-        <v>138.84</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -10090,22 +10090,22 @@
         <v>0.115</v>
       </c>
       <c r="D36">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="E36">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="F36">
-        <v>105.3</v>
+        <v>114.4</v>
       </c>
       <c r="G36">
-        <v>112.58</v>
+        <v>122.2</v>
       </c>
       <c r="H36">
-        <v>126.36</v>
+        <v>137.28</v>
       </c>
       <c r="I36">
-        <v>135.1</v>
+        <v>146.64</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -10119,22 +10119,22 @@
         <v>0.104</v>
       </c>
       <c r="D37">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="E37">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="F37">
-        <v>76.44</v>
+        <v>83.2</v>
       </c>
       <c r="G37">
-        <v>81.90000000000001</v>
+        <v>88.92</v>
       </c>
       <c r="H37">
-        <v>91.73</v>
+        <v>99.84</v>
       </c>
       <c r="I37">
-        <v>98.28</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -10148,22 +10148,22 @@
         <v>0.096</v>
       </c>
       <c r="D38">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="E38">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F38">
-        <v>61.36</v>
+        <v>66.56</v>
       </c>
       <c r="G38">
-        <v>65.78</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="H38">
-        <v>73.63</v>
+        <v>79.87</v>
       </c>
       <c r="I38">
-        <v>78.94</v>
+        <v>85.48999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -10177,22 +10177,22 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D39">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E39">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F39">
-        <v>39.78</v>
+        <v>43.16</v>
       </c>
       <c r="G39">
-        <v>42.9</v>
+        <v>46.28</v>
       </c>
       <c r="H39">
-        <v>47.74</v>
+        <v>51.79</v>
       </c>
       <c r="I39">
-        <v>51.48</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -10206,22 +10206,22 @@
         <v>0.08199999999999999</v>
       </c>
       <c r="D40">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E40">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F40">
-        <v>37.7</v>
+        <v>41.08</v>
       </c>
       <c r="G40">
-        <v>40.82</v>
+        <v>44.2</v>
       </c>
       <c r="H40">
-        <v>45.24</v>
+        <v>49.3</v>
       </c>
       <c r="I40">
-        <v>48.98</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -10235,22 +10235,22 @@
         <v>0.063</v>
       </c>
       <c r="D41">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E41">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="F41">
-        <v>46.8</v>
+        <v>50.96</v>
       </c>
       <c r="G41">
-        <v>50.96</v>
+        <v>55.12</v>
       </c>
       <c r="H41">
-        <v>56.16</v>
+        <v>61.15</v>
       </c>
       <c r="I41">
-        <v>61.15</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -10264,22 +10264,22 @@
         <v>0.062</v>
       </c>
       <c r="D42">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E42">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F42">
-        <v>11.18</v>
+        <v>12.22</v>
       </c>
       <c r="G42">
-        <v>12.22</v>
+        <v>13.52</v>
       </c>
       <c r="H42">
-        <v>13.42</v>
+        <v>14.66</v>
       </c>
       <c r="I42">
-        <v>14.66</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -10293,22 +10293,22 @@
         <v>0.051</v>
       </c>
       <c r="D43">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E43">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F43">
-        <v>16.64</v>
+        <v>17.94</v>
       </c>
       <c r="G43">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="H43">
-        <v>19.97</v>
+        <v>21.53</v>
       </c>
       <c r="I43">
-        <v>21.84</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -10322,22 +10322,22 @@
         <v>0.032</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44">
-        <v>4.16</v>
+        <v>4.42</v>
       </c>
       <c r="G44">
-        <v>4.68</v>
+        <v>4.94</v>
       </c>
       <c r="H44">
-        <v>4.99</v>
+        <v>5.3</v>
       </c>
       <c r="I44">
-        <v>5.62</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -10351,22 +10351,22 @@
         <v>0.016</v>
       </c>
       <c r="D45">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E45">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F45">
-        <v>15.08</v>
+        <v>16.12</v>
       </c>
       <c r="G45">
-        <v>16.38</v>
+        <v>17.68</v>
       </c>
       <c r="H45">
-        <v>18.1</v>
+        <v>19.34</v>
       </c>
       <c r="I45">
-        <v>19.66</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -10380,22 +10380,22 @@
         <v>0.016</v>
       </c>
       <c r="D46">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E46">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F46">
-        <v>10.14</v>
+        <v>11.18</v>
       </c>
       <c r="G46">
-        <v>11.44</v>
+        <v>12.48</v>
       </c>
       <c r="H46">
-        <v>12.17</v>
+        <v>13.42</v>
       </c>
       <c r="I46">
-        <v>13.73</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -10492,22 +10492,22 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
-        <v>7798</v>
+        <v>7300</v>
       </c>
       <c r="E50" s="2">
-        <v>8358</v>
+        <v>7823</v>
       </c>
       <c r="F50" s="2">
-        <v>3047.14</v>
+        <v>2782</v>
       </c>
       <c r="G50" s="2">
-        <v>3263.4</v>
+        <v>2980</v>
       </c>
       <c r="H50" s="2">
-        <v>3656.57</v>
+        <v>3338.4</v>
       </c>
       <c r="I50" s="2">
-        <v>3916.08</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -10652,37 +10652,37 @@
         <v>121</v>
       </c>
       <c r="B7">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D7">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F7">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="G7">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="H7">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I7">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
         <v>6</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -10694,7 +10694,7 @@
         <v>2</v>
       </c>
       <c r="P7">
-        <v>560</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -10702,40 +10702,40 @@
         <v>122</v>
       </c>
       <c r="B8">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F8">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="G8">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H8">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I8">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>2</v>
@@ -10744,7 +10744,7 @@
         <v>2</v>
       </c>
       <c r="P8">
-        <v>463</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -10752,28 +10752,28 @@
         <v>123</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E9">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F9">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G9">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="H9">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>273</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -10802,34 +10802,34 @@
         <v>124</v>
       </c>
       <c r="B10">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D10">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E10">
+        <v>83</v>
+      </c>
+      <c r="F10">
+        <v>87</v>
+      </c>
+      <c r="G10">
         <v>94</v>
       </c>
-      <c r="F10">
-        <v>101</v>
-      </c>
-      <c r="G10">
-        <v>107</v>
-      </c>
       <c r="H10">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J10">
         <v>2</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -10844,7 +10844,7 @@
         <v>2</v>
       </c>
       <c r="P10">
-        <v>293</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -10852,25 +10852,25 @@
         <v>125</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
         <v>11</v>
       </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
       <c r="F11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -10894,7 +10894,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -10902,28 +10902,28 @@
         <v>126</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F12">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H12">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -10944,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -10952,31 +10952,31 @@
         <v>127</v>
       </c>
       <c r="B13">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C13">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D13">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="E13">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="G13">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="H13">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I13">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -10985,7 +10985,7 @@
         <v>3</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -10994,7 +10994,7 @@
         <v>2</v>
       </c>
       <c r="P13">
-        <v>455</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -11002,34 +11002,34 @@
         <v>128</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D14">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E14">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F14">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G14">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H14">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I14">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="J14">
         <v>2</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -11044,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>281</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -11052,28 +11052,28 @@
         <v>129</v>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D15">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E15">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F15">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G15">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H15">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -11094,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>270</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -11102,40 +11102,40 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="C16" s="2">
-        <v>414</v>
+        <v>359</v>
       </c>
       <c r="D16" s="2">
-        <v>845</v>
+        <v>733</v>
       </c>
       <c r="E16" s="2">
-        <v>900</v>
+        <v>780</v>
       </c>
       <c r="F16" s="2">
-        <v>946</v>
+        <v>821</v>
       </c>
       <c r="G16" s="2">
-        <v>1007</v>
+        <v>875</v>
       </c>
       <c r="H16" s="2">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="I16" s="2">
-        <v>567</v>
+        <v>493</v>
       </c>
       <c r="J16" s="2">
+        <v>22</v>
+      </c>
+      <c r="K16" s="2">
         <v>25</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
+        <v>23</v>
+      </c>
+      <c r="M16" s="2">
         <v>28</v>
-      </c>
-      <c r="L16" s="2">
-        <v>25</v>
-      </c>
-      <c r="M16" s="2">
-        <v>30</v>
       </c>
       <c r="N16" s="2">
         <v>6</v>
@@ -11144,7 +11144,7 @@
         <v>8</v>
       </c>
       <c r="P16" s="2">
-        <v>2764</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -11168,7 +11168,7 @@
         <v>121</v>
       </c>
       <c r="B20">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="C20">
         <v>198</v>
@@ -11179,7 +11179,7 @@
         <v>122</v>
       </c>
       <c r="B21">
-        <v>463</v>
+        <v>403</v>
       </c>
       <c r="C21">
         <v>164</v>
@@ -11190,7 +11190,7 @@
         <v>123</v>
       </c>
       <c r="B22">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="C22">
         <v>99.2</v>
@@ -11201,7 +11201,7 @@
         <v>124</v>
       </c>
       <c r="B23">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="C23">
         <v>104.8</v>
@@ -11212,7 +11212,7 @@
         <v>125</v>
       </c>
       <c r="B24">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -11223,7 +11223,7 @@
         <v>126</v>
       </c>
       <c r="B25">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>48.7</v>
@@ -11234,7 +11234,7 @@
         <v>127</v>
       </c>
       <c r="B26">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="C26">
         <v>164</v>
@@ -11245,7 +11245,7 @@
         <v>128</v>
       </c>
       <c r="B27">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="C27">
         <v>100.8</v>
@@ -11256,7 +11256,7 @@
         <v>129</v>
       </c>
       <c r="B28">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="C28">
         <v>99</v>
@@ -11335,37 +11335,37 @@
         <v>121</v>
       </c>
       <c r="B34">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C34">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D34">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="E34">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="F34">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="G34">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="H34">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I34">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>489</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -11373,37 +11373,37 @@
         <v>122</v>
       </c>
       <c r="B35">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C35">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D35">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="E35">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="F35">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G35">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="H35">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I35">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>396</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -11411,37 +11411,37 @@
         <v>123</v>
       </c>
       <c r="B36">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C36">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D36">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E36">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F36">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G36">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H36">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I36">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36">
-        <v>261</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -11449,37 +11449,37 @@
         <v>124</v>
       </c>
       <c r="B37">
+        <v>53</v>
+      </c>
+      <c r="C37">
         <v>59</v>
       </c>
-      <c r="C37">
-        <v>64</v>
-      </c>
       <c r="D37">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E37">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F37">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G37">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="H37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I37">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37">
         <v>4</v>
       </c>
       <c r="L37">
-        <v>280</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -11487,22 +11487,22 @@
         <v>125</v>
       </c>
       <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
         <v>5</v>
       </c>
-      <c r="C38">
-        <v>7</v>
-      </c>
       <c r="D38">
+        <v>9</v>
+      </c>
+      <c r="E38">
         <v>10</v>
-      </c>
-      <c r="E38">
-        <v>11</v>
       </c>
       <c r="F38">
         <v>9</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -11517,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -11525,37 +11525,37 @@
         <v>126</v>
       </c>
       <c r="B39">
+        <v>37</v>
+      </c>
+      <c r="C39">
         <v>40</v>
       </c>
-      <c r="C39">
-        <v>45</v>
-      </c>
       <c r="D39">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E39">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F39">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G39">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H39">
         <v>12</v>
       </c>
       <c r="I39">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39">
-        <v>196</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -11563,37 +11563,37 @@
         <v>127</v>
       </c>
       <c r="B40">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C40">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D40">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E40">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F40">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G40">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H40">
+        <v>21</v>
+      </c>
+      <c r="I40">
         <v>24</v>
-      </c>
-      <c r="I40">
-        <v>28</v>
       </c>
       <c r="J40">
         <v>5</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>388</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -11601,37 +11601,37 @@
         <v>128</v>
       </c>
       <c r="B41">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C41">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D41">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E41">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F41">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="H41">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I41">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41">
-        <v>271</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -11639,37 +11639,37 @@
         <v>129</v>
       </c>
       <c r="B42">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C42">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D42">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E42">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F42">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G42">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H42">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I42">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J42">
         <v>3</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>238</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -11677,37 +11677,37 @@
         <v>13</v>
       </c>
       <c r="B43" s="2">
-        <v>538</v>
+        <v>465</v>
       </c>
       <c r="C43" s="2">
-        <v>578</v>
+        <v>499</v>
       </c>
       <c r="D43" s="2">
-        <v>920</v>
+        <v>795</v>
       </c>
       <c r="E43" s="2">
-        <v>982</v>
+        <v>850</v>
       </c>
       <c r="F43" s="2">
-        <v>887</v>
+        <v>767</v>
       </c>
       <c r="G43" s="2">
-        <v>948</v>
+        <v>820</v>
       </c>
       <c r="H43" s="2">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I43" s="2">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="J43" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K43" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2">
-        <v>2545</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -11731,7 +11731,7 @@
         <v>121</v>
       </c>
       <c r="B47">
-        <v>489</v>
+        <v>425</v>
       </c>
       <c r="C47">
         <v>151.2</v>
@@ -11742,7 +11742,7 @@
         <v>122</v>
       </c>
       <c r="B48">
-        <v>396</v>
+        <v>346</v>
       </c>
       <c r="C48">
         <v>121.8</v>
@@ -11753,7 +11753,7 @@
         <v>123</v>
       </c>
       <c r="B49">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="C49">
         <v>81.90000000000001</v>
@@ -11764,7 +11764,7 @@
         <v>124</v>
       </c>
       <c r="B50">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="C50">
         <v>86.3</v>
@@ -11775,7 +11775,7 @@
         <v>125</v>
       </c>
       <c r="B51">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C51">
         <v>8.699999999999999</v>
@@ -11786,7 +11786,7 @@
         <v>126</v>
       </c>
       <c r="B52">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C52">
         <v>62.5</v>
@@ -11797,7 +11797,7 @@
         <v>127</v>
       </c>
       <c r="B53">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="C53">
         <v>121.8</v>
@@ -11808,7 +11808,7 @@
         <v>128</v>
       </c>
       <c r="B54">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="C54">
         <v>83.7</v>
@@ -11819,7 +11819,7 @@
         <v>129</v>
       </c>
       <c r="B55">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="C55">
         <v>75.59999999999999</v>
@@ -11918,49 +11918,49 @@
         <v>121</v>
       </c>
       <c r="B61">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C61">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D61">
+        <v>69</v>
+      </c>
+      <c r="E61">
+        <v>72</v>
+      </c>
+      <c r="F61">
+        <v>76</v>
+      </c>
+      <c r="G61">
+        <v>82</v>
+      </c>
+      <c r="H61">
         <v>64</v>
       </c>
-      <c r="E61">
-        <v>67</v>
-      </c>
-      <c r="F61">
+      <c r="I61">
         <v>70</v>
       </c>
-      <c r="G61">
-        <v>75</v>
-      </c>
-      <c r="H61">
-        <v>59</v>
-      </c>
-      <c r="I61">
-        <v>63</v>
-      </c>
       <c r="J61">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K61">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L61">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M61">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="N61">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O61">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P61">
-        <v>453</v>
+        <v>487</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -11968,49 +11968,49 @@
         <v>122</v>
       </c>
       <c r="B62">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C62">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D62">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E62">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F62">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G62">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H62">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I62">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J62">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K62">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L62">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="M62">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N62">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O62">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P62">
-        <v>420</v>
+        <v>456</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -12018,49 +12018,49 @@
         <v>123</v>
       </c>
       <c r="B63">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C63">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D63">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E63">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F63">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G63">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H63">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I63">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J63">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K63">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L63">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M63">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N63">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O63">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="P63">
-        <v>356</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -12068,49 +12068,49 @@
         <v>124</v>
       </c>
       <c r="B64">
+        <v>30</v>
+      </c>
+      <c r="C64">
+        <v>33</v>
+      </c>
+      <c r="D64">
+        <v>31</v>
+      </c>
+      <c r="E64">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>37</v>
+      </c>
+      <c r="G64">
+        <v>41</v>
+      </c>
+      <c r="H64">
+        <v>33</v>
+      </c>
+      <c r="I64">
+        <v>35</v>
+      </c>
+      <c r="J64">
         <v>29</v>
       </c>
-      <c r="C64">
-        <v>30</v>
-      </c>
-      <c r="D64">
-        <v>29</v>
-      </c>
-      <c r="E64">
+      <c r="K64">
         <v>31</v>
       </c>
-      <c r="F64">
-        <v>33</v>
-      </c>
-      <c r="G64">
-        <v>36</v>
-      </c>
-      <c r="H64">
-        <v>28</v>
-      </c>
-      <c r="I64">
-        <v>33</v>
-      </c>
-      <c r="J64">
-        <v>26</v>
-      </c>
-      <c r="K64">
-        <v>29</v>
-      </c>
       <c r="L64">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M64">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N64">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O64">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P64">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -12124,16 +12124,16 @@
         <v>6</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H65">
         <v>6</v>
@@ -12148,19 +12148,19 @@
         <v>5</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M65">
+        <v>8</v>
+      </c>
+      <c r="N65">
+        <v>6</v>
+      </c>
+      <c r="O65">
         <v>7</v>
       </c>
-      <c r="N65">
-        <v>7</v>
-      </c>
-      <c r="O65">
-        <v>6</v>
-      </c>
       <c r="P65">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -12171,46 +12171,46 @@
         <v>17</v>
       </c>
       <c r="C66">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66">
+        <v>20</v>
+      </c>
+      <c r="E66">
+        <v>22</v>
+      </c>
+      <c r="F66">
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <v>23</v>
+      </c>
+      <c r="H66">
         <v>19</v>
       </c>
-      <c r="E66">
+      <c r="I66">
         <v>20</v>
       </c>
-      <c r="F66">
-        <v>20</v>
-      </c>
-      <c r="G66">
-        <v>20</v>
-      </c>
-      <c r="H66">
-        <v>18</v>
-      </c>
-      <c r="I66">
+      <c r="J66">
         <v>19</v>
       </c>
-      <c r="J66">
-        <v>17</v>
-      </c>
       <c r="K66">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L66">
         <v>20</v>
       </c>
       <c r="M66">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N66">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O66">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P66">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -12218,49 +12218,49 @@
         <v>127</v>
       </c>
       <c r="B67">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C67">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D67">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E67">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F67">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G67">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H67">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I67">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J67">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K67">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L67">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M67">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N67">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="O67">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P67">
-        <v>409</v>
+        <v>443</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -12268,49 +12268,49 @@
         <v>128</v>
       </c>
       <c r="B68">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C68">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D68">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E68">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F68">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G68">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H68">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I68">
         <v>36</v>
       </c>
       <c r="J68">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K68">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L68">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M68">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N68">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O68">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P68">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -12318,49 +12318,49 @@
         <v>129</v>
       </c>
       <c r="B69">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C69">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D69">
+        <v>33</v>
+      </c>
+      <c r="E69">
+        <v>39</v>
+      </c>
+      <c r="F69">
+        <v>40</v>
+      </c>
+      <c r="G69">
+        <v>42</v>
+      </c>
+      <c r="H69">
+        <v>33</v>
+      </c>
+      <c r="I69">
+        <v>36</v>
+      </c>
+      <c r="J69">
         <v>30</v>
       </c>
-      <c r="E69">
-        <v>35</v>
-      </c>
-      <c r="F69">
-        <v>35</v>
-      </c>
-      <c r="G69">
-        <v>40</v>
-      </c>
-      <c r="H69">
-        <v>32</v>
-      </c>
-      <c r="I69">
+      <c r="K69">
         <v>33</v>
-      </c>
-      <c r="J69">
-        <v>27</v>
-      </c>
-      <c r="K69">
-        <v>30</v>
       </c>
       <c r="L69">
         <v>35</v>
       </c>
       <c r="M69">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N69">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O69">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P69">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -12368,49 +12368,49 @@
         <v>13</v>
       </c>
       <c r="B70" s="2">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="C70" s="2">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="D70" s="2">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="E70" s="2">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="F70" s="2">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="G70" s="2">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="H70" s="2">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="I70" s="2">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="J70" s="2">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="K70" s="2">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="L70" s="2">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="M70" s="2">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="N70" s="2">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="O70" s="2">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="P70" s="2">
-        <v>2489</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -12434,7 +12434,7 @@
         <v>121</v>
       </c>
       <c r="B74">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="C74">
         <v>116.6</v>
@@ -12445,7 +12445,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="C75">
         <v>106.5</v>
@@ -12456,7 +12456,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="C76">
         <v>93.2</v>
@@ -12467,7 +12467,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C77">
         <v>57</v>
@@ -12478,7 +12478,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C78">
         <v>10.1</v>
@@ -12489,7 +12489,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C79">
         <v>34.5</v>
@@ -12500,7 +12500,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="C80">
         <v>106.5</v>
@@ -12511,7 +12511,7 @@
         <v>128</v>
       </c>
       <c r="B81">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C81">
         <v>62.4</v>
@@ -12522,7 +12522,7 @@
         <v>129</v>
       </c>
       <c r="B82">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C82">
         <v>58.3</v>
